--- a/tests/reports/Vulnerability_Test_Report_BrainBattle_2026-06-15T10-37-33.xlsx
+++ b/tests/reports/Vulnerability_Test_Report_BrainBattle_2026-06-15T10-37-33.xlsx
@@ -18,13 +18,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
     </font>
   </fonts>
   <fills count="2">
@@ -47,8 +51,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -452,9 +457,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -462,9 +467,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -798,9 +803,9 @@
           <t>requirements.txt</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Flask version is slightly outdated (non-critical update available)</t>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
